--- a/backtest_runs/20260410_193731/by_symbol/PGLC/PGLC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PGLC/PGLC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-9800.639999999989</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>94103.68000000001</v>
@@ -817,7 +817,7 @@
         <v>-6932.159999999993</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>100717.12</v>
@@ -909,7 +909,7 @@
         <v>-876.4800000000096</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>99840.64</v>
@@ -955,7 +955,7 @@
         <v>-4940.159999999993</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>94900.48000000001</v>
@@ -1047,7 +1047,7 @@
         <v>-478.0799999999898</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>96095.68000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-7410.239999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>97370.56000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-7489.919999999996</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>98167.36000000002</v>
@@ -1369,7 +1369,7 @@
         <v>-1434.239999999998</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>96733.12000000001</v>
@@ -1507,7 +1507,7 @@
         <v>-4860.48000000001</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>96573.76000000001</v>
@@ -1553,7 +1553,7 @@
         <v>-478.0799999999898</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>96095.68000000001</v>
